--- a/examples/wheeled-swarm/engineering/swarm-robot-calcs.xlsx
+++ b/examples/wheeled-swarm/engineering/swarm-robot-calcs.xlsx
@@ -598,7 +598,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" s="9">
         <f>B6*C6</f>
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D7" s="9">
         <f>B7*C7</f>
@@ -659,14 +659,14 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>VL53L0X distance sensor</t>
+          <t>HC-SR04 ultrasonic sensor</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>1.5</v>
+        <v>9</v>
       </c>
       <c r="D10" s="9">
         <f>B10*C10</f>
@@ -676,7 +676,7 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Ball caster</t>
+          <t>Wiring / connectors</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
@@ -693,14 +693,14 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Wiring / connectors</t>
+          <t>ArUco tag (paper)</t>
         </is>
       </c>
       <c r="B12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="D12" s="9">
         <f>B12*C12</f>
@@ -708,58 +708,41 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>ArUco tag (paper)</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Dry mass (no battery)</t>
+        </is>
+      </c>
+      <c r="D13" s="11">
+        <f>SUM(D6:D12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Battery (4×AA holder + cells)</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D13" s="9">
-        <f>B13*C13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>Dry mass (no battery)</t>
-        </is>
-      </c>
-      <c r="D14" s="11">
-        <f>SUM(D6:D13)</f>
+      <c r="C14" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D14" s="9">
+        <f>B14*C14</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Battery (4×AA holder + cells)</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="D15" s="9">
-        <f>B15*C15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>ALL-UP MASS</t>
         </is>
       </c>
-      <c r="D16" s="13">
-        <f>D14+D15</f>
+      <c r="D15" s="13">
+        <f>D13+D14</f>
         <v/>
       </c>
     </row>
@@ -901,7 +884,7 @@
         </is>
       </c>
       <c r="B25" s="18">
-        <f>B22*D16/1000*9.81</f>
+        <f>B22*D15/1000*9.81</f>
         <v/>
       </c>
       <c r="C25" s="14" t="inlineStr">
@@ -986,7 +969,7 @@
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C31" s="14" t="inlineStr"/>
     </row>
